--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -38,6 +38,12 @@
     <t>result_id</t>
   </si>
   <si>
+    <t>effects</t>
+  </si>
+  <si>
+    <t>effectValuePos</t>
+  </si>
+  <si>
     <t>requireTag</t>
   </si>
   <si>
@@ -65,7 +71,13 @@
     <t>int</t>
   </si>
   <si>
-    <t>TileType</t>
+    <t>TileStateType</t>
+  </si>
+  <si>
+    <t>(list#sep=;),TileEffectType</t>
+  </si>
+  <si>
+    <t>(list#sep=;),int</t>
   </si>
   <si>
     <t>ElementTag</t>
@@ -89,7 +101,10 @@
     <t>优先级</t>
   </si>
   <si>
-    <t>对应结果ID</t>
+    <t>对应生成的地形</t>
+  </si>
+  <si>
+    <t>生成的效果</t>
   </si>
   <si>
     <t>必须有的标签</t>
@@ -116,6 +131,9 @@
     <t>蒸汽</t>
   </si>
   <si>
+    <t>击退</t>
+  </si>
+  <si>
     <t>含土|含沙|含植物</t>
   </si>
   <si>
@@ -125,6 +143,9 @@
     <t>稀泥</t>
   </si>
   <si>
+    <t>滑行</t>
+  </si>
+  <si>
     <t>含土</t>
   </si>
   <si>
@@ -137,6 +158,12 @@
     <t>燃烧</t>
   </si>
   <si>
+    <t>击退;清除植物</t>
+  </si>
+  <si>
+    <t>1;1</t>
+  </si>
+  <si>
     <t>含植物</t>
   </si>
   <si>
@@ -155,12 +182,18 @@
     <t>玻璃</t>
   </si>
   <si>
+    <t>击退;瞬时伤害</t>
+  </si>
+  <si>
     <t>结冰</t>
   </si>
   <si>
     <t>基础水地块</t>
   </si>
   <si>
+    <t>温湿度继承</t>
+  </si>
+  <si>
     <t>基础土地块</t>
   </si>
   <si>
@@ -174,6 +207,9 @@
   </si>
   <si>
     <t>基础电源</t>
+  </si>
+  <si>
+    <t>无</t>
   </si>
 </sst>
 </file>
@@ -800,12 +836,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1341,15 +1380,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="3" max="3" width="14.3545454545455" customWidth="1"/>
-    <col min="4" max="4" width="16.5090909090909" customWidth="1"/>
-    <col min="5" max="5" width="19.6181818181818" customWidth="1"/>
+    <col min="3" max="4" width="14.3545454545455" customWidth="1"/>
+    <col min="5" max="6" width="16.5090909090909" customWidth="1"/>
+    <col min="7" max="7" width="19.6181818181818" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1407,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1380,149 +1419,173 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:12">
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="1">
         <v>4</v>
       </c>
-      <c r="G5" s="1">
-        <v>6</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
+        <v>6</v>
+      </c>
+      <c r="J5" s="1">
         <v>2</v>
       </c>
-      <c r="I5" s="1">
-        <v>6</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
+        <v>6</v>
+      </c>
+      <c r="L5" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:12">
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="1">
         <v>-2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>6</v>
-      </c>
-      <c r="H6" s="1">
-        <v>2</v>
       </c>
       <c r="I6" s="1">
         <v>6</v>
@@ -1530,423 +1593,512 @@
       <c r="J6" s="1">
         <v>2</v>
       </c>
+      <c r="K6" s="1">
+        <v>6</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:12">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="C7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="1">
         <v>-1</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="1">
+      <c r="J7" s="1">
         <v>5</v>
       </c>
-      <c r="I7" s="1">
-        <v>6</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
+        <v>6</v>
+      </c>
+      <c r="L7" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:12">
       <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="C8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="1">
         <v>-1</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>2</v>
       </c>
-      <c r="H8" s="1">
+      <c r="J8" s="1">
         <v>3</v>
       </c>
-      <c r="I8" s="1">
+      <c r="K8" s="1">
         <v>4</v>
       </c>
-      <c r="J8" s="1">
+      <c r="L8" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:12">
       <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1">
+      <c r="C9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1">
         <v>4</v>
       </c>
-      <c r="G9" s="1">
-        <v>6</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="1">
-        <v>6</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
+        <v>6</v>
+      </c>
+      <c r="L9" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:12">
       <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="C10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1">
+      <c r="F10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1">
         <v>-6</v>
       </c>
-      <c r="G10" s="1">
-        <v>6</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="1">
-        <v>6</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
+        <v>6</v>
+      </c>
+      <c r="L10" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:12">
       <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="C11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="1">
         <v>3</v>
       </c>
-      <c r="G11" s="1">
-        <v>6</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
         <v>0</v>
       </c>
-      <c r="I11" s="1">
-        <v>6</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
+        <v>6</v>
+      </c>
+      <c r="L11" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:12">
       <c r="B12" s="1">
         <v>8</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="1">
         <v>-6</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>-2</v>
       </c>
-      <c r="H12" s="1">
+      <c r="J12" s="1">
         <v>2</v>
       </c>
-      <c r="I12" s="1">
-        <v>6</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
+        <v>6</v>
+      </c>
+      <c r="L12" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:12">
       <c r="B13" s="1">
         <v>9</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1">
         <v>-6</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>-1</v>
       </c>
-      <c r="H13" s="1">
+      <c r="J13" s="1">
         <v>2</v>
       </c>
-      <c r="I13" s="1">
-        <v>6</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
+        <v>6</v>
+      </c>
+      <c r="L13" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:12">
       <c r="B14" s="1">
         <v>10</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1">
+      <c r="C14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1">
         <v>3</v>
       </c>
-      <c r="G14" s="1">
-        <v>6</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
+        <v>6</v>
+      </c>
+      <c r="J14" s="1">
         <v>0</v>
       </c>
-      <c r="I14" s="1">
-        <v>6</v>
-      </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
+        <v>6</v>
+      </c>
+      <c r="L14" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:12">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="C15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="1">
         <v>-6</v>
       </c>
-      <c r="G15" s="1">
+      <c r="I15" s="1">
         <v>-2</v>
       </c>
-      <c r="H15" s="1">
+      <c r="J15" s="1">
         <v>2</v>
       </c>
-      <c r="I15" s="1">
-        <v>6</v>
-      </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
+        <v>6</v>
+      </c>
+      <c r="L15" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:12">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="1">
+      <c r="C16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="1">
         <v>-6</v>
       </c>
-      <c r="G16" s="1">
-        <v>6</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
+        <v>6</v>
+      </c>
+      <c r="J16" s="1">
         <v>2</v>
       </c>
-      <c r="I16" s="1">
-        <v>6</v>
-      </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
+        <v>6</v>
+      </c>
+      <c r="L16" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:12">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>13</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="1">
+      <c r="C17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="1">
         <v>-6</v>
       </c>
-      <c r="G17" s="1">
-        <v>6</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
+        <v>6</v>
+      </c>
+      <c r="J17" s="1">
         <v>0</v>
       </c>
-      <c r="I17" s="1">
+      <c r="K17" s="1">
         <v>2</v>
       </c>
-      <c r="J17" s="1">
+      <c r="L17" s="1">
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:12">
       <c r="B18" s="1">
         <v>14</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="C18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="4">
         <v>4</v>
       </c>
-      <c r="G18" s="3">
-        <v>6</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="4">
+        <v>6</v>
+      </c>
+      <c r="J18" s="4">
         <v>0</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="4">
         <v>1</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:12">
       <c r="B19" s="1">
         <v>15</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="3">
+      <c r="C19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="4">
         <v>-6</v>
       </c>
-      <c r="G19" s="3">
+      <c r="I19" s="4">
         <v>-4</v>
       </c>
-      <c r="H19" s="3">
+      <c r="J19" s="4">
         <v>0</v>
       </c>
-      <c r="I19" s="3">
+      <c r="K19" s="4">
         <v>1</v>
       </c>
-      <c r="J19" s="3">
+      <c r="L19" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:12">
       <c r="B20" s="1">
         <v>16</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3">
+      <c r="C20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4">
         <v>-6</v>
       </c>
-      <c r="G20" s="3">
-        <v>6</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="4">
+        <v>6</v>
+      </c>
+      <c r="J20" s="4">
         <v>0</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="4">
         <v>1</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:12">
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="C21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="4">
         <v>1</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="4">
         <v>1</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="4">
         <v>0</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="4">
         <v>1</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="1">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>-6</v>
+      </c>
+      <c r="I22" s="1">
+        <v>6</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>6</v>
+      </c>
+      <c r="L22" s="1">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>

--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF31411-07B8-4C7C-8772-A799325E5D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6512BD9D-709E-4BD2-BC9F-F34A6D16F15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3225" yWindow="4260" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -115,13 +115,42 @@
   </si>
   <si>
     <t>TRUE</t>
+  </si>
+  <si>
+    <t>impact_radius</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>loat</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>波及范围(格)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +161,14 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -158,8 +195,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -642,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
@@ -650,10 +690,10 @@
     <col min="5" max="6" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -679,10 +719,13 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -707,11 +750,14 @@
       <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -736,11 +782,14 @@
       <c r="H3" t="s">
         <v>16</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -765,11 +814,14 @@
       <c r="H4" t="s">
         <v>24</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B5">
         <v>1</v>
       </c>
@@ -791,11 +843,14 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6">
         <v>2</v>
       </c>
@@ -817,11 +872,14 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7">
         <v>3</v>
       </c>
@@ -843,11 +901,14 @@
       <c r="H7">
         <v>0</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7">
+        <v>1.5</v>
+      </c>
+      <c r="J7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8">
         <v>4</v>
       </c>
@@ -869,11 +930,14 @@
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8">
+        <v>1.5</v>
+      </c>
+      <c r="J8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B9">
         <v>5</v>
       </c>
@@ -895,11 +959,14 @@
       <c r="H9">
         <v>0</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10">
         <v>6</v>
       </c>
@@ -921,11 +988,14 @@
       <c r="H10">
         <v>1.5</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11">
         <v>7</v>
       </c>
@@ -947,11 +1017,14 @@
       <c r="H11">
         <v>0</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11">
+        <v>1.5</v>
+      </c>
+      <c r="J11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12">
         <v>8</v>
       </c>
@@ -973,11 +1046,14 @@
       <c r="H12">
         <v>0</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13">
         <v>9</v>
       </c>
@@ -999,11 +1075,14 @@
       <c r="H13">
         <v>0</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14">
         <v>10</v>
       </c>
@@ -1025,11 +1104,14 @@
       <c r="H14">
         <v>0</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15">
         <v>11</v>
       </c>
@@ -1051,12 +1133,16 @@
       <c r="H15">
         <v>0</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6512BD9D-709E-4BD2-BC9F-F34A6D16F15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A567719-623E-4776-BC81-993A5B179121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3225" yWindow="4260" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -105,13 +105,7 @@
     <t>触发网格连锁</t>
   </si>
   <si>
-    <t>Water</t>
-  </si>
-  <si>
     <t>FALSE</t>
-  </si>
-  <si>
-    <t>Earth</t>
   </si>
   <si>
     <t>TRUE</t>
@@ -143,6 +137,56 @@
   </si>
   <si>
     <t>波及范围(格)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础水</t>
+  </si>
+  <si>
+    <t>基础水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纯水</t>
+  </si>
+  <si>
+    <t>纯土</t>
+  </si>
+  <si>
+    <t>普通泥浆</t>
+  </si>
+  <si>
+    <t>基础火池</t>
+  </si>
+  <si>
+    <t>空地</t>
+  </si>
+  <si>
+    <t>稀泥</t>
+  </si>
+  <si>
+    <t>基础电源</t>
+  </si>
+  <si>
+    <t>基础冰面</t>
+  </si>
+  <si>
+    <t>基础植物区</t>
+  </si>
+  <si>
+    <t>基础土</t>
+  </si>
+  <si>
+    <t>蒸汽</t>
+  </si>
+  <si>
+    <t>陶砖</t>
+  </si>
+  <si>
+    <t>结冰</t>
+  </si>
+  <si>
+    <t>导电区</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -683,17 +727,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -719,13 +763,13 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -751,13 +795,13 @@
         <v>13</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -783,13 +827,13 @@
         <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -815,53 +859,53 @@
         <v>24</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>15</v>
+      <c r="C5" t="s">
+        <v>43</v>
       </c>
       <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>26</v>
       </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6">
-        <v>14</v>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -876,21 +920,21 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>2</v>
+      <c r="C7" t="s">
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -905,21 +949,21 @@
         <v>1.5</v>
       </c>
       <c r="J7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8">
-        <v>16</v>
+      <c r="C8" t="s">
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8">
-        <v>8</v>
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
       </c>
       <c r="F8">
         <v>2</v>
@@ -934,21 +978,21 @@
         <v>1.5</v>
       </c>
       <c r="J8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9">
-        <v>16</v>
+      <c r="C9" t="s">
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9">
-        <v>6</v>
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -963,21 +1007,21 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10">
-        <v>18</v>
+      <c r="C10" t="s">
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10">
-        <v>20</v>
+        <v>34</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -992,21 +1036,21 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>7</v>
       </c>
-      <c r="C11">
-        <v>17</v>
+      <c r="C11" t="s">
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1021,50 +1065,50 @@
         <v>1.5</v>
       </c>
       <c r="J11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>8</v>
       </c>
-      <c r="C12">
-        <v>19</v>
+      <c r="C12" t="s">
+        <v>42</v>
       </c>
       <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
         <v>26</v>
       </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>9</v>
       </c>
-      <c r="C13">
-        <v>2</v>
+      <c r="C13" t="s">
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1079,50 +1123,50 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>10</v>
       </c>
-      <c r="C14">
-        <v>1</v>
+      <c r="C14" t="s">
+        <v>38</v>
       </c>
       <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
         <v>26</v>
       </c>
-      <c r="E14">
-        <v>14</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>11</v>
       </c>
-      <c r="C15">
-        <v>1</v>
+      <c r="C15" t="s">
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15">
-        <v>15</v>
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1137,11 +1181,16 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576 E1:E1048576" xr:uid="{3185D381-DA91-4C4E-B871-4CFF429EC902}">
+      <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A567719-623E-4776-BC81-993A5B179121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A276CE7-AE51-411A-8C13-2EFACBF0BBC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -239,12 +239,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -726,469 +729,560 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
         <v>1.5</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>2</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
         <v>1.5</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
         <v>1.5</v>
       </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
         <v>3</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
         <v>1.5</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B12">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B12" s="1">
         <v>8</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B13">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B13" s="1">
         <v>9</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B14" s="1">
         <v>10</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B15" s="1">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B16" s="1">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B17" s="1">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B15">
-        <v>11</v>
-      </c>
-      <c r="C15" t="s">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B18" s="1">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576 E1:E1048576" xr:uid="{3185D381-DA91-4C4E-B871-4CFF429EC902}">
       <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{C7F4E47B-FBE5-41F6-8965-69779C735560}">
+      <formula1>"纯水,纯土"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A276CE7-AE51-411A-8C13-2EFACBF0BBC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E593674-59EC-4505-9460-EBC7FA908D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>

--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E593674-59EC-4505-9460-EBC7FA908D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="14940" windowHeight="9900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -51,6 +53,9 @@
     <t>impact_stun</t>
   </si>
   <si>
+    <t>impact_radius</t>
+  </si>
+  <si>
     <t>trigger_chain</t>
   </si>
   <si>
@@ -69,53 +74,14 @@
     <t>float</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>原格状态</t>
-  </si>
-  <si>
-    <t>投入小球</t>
-  </si>
-  <si>
-    <t>生成地貌</t>
-  </si>
-  <si>
-    <t>瞬时伤害</t>
-  </si>
-  <si>
-    <t>击退距离(格)</t>
-  </si>
-  <si>
-    <t>麻痹时间(秒)</t>
-  </si>
-  <si>
-    <t>触发网格连锁</t>
-  </si>
-  <si>
-    <t>FALSE</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>impact_radius</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>f</t>
     </r>
     <r>
@@ -123,78 +89,114 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>loat</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>##group</t>
   </si>
   <si>
     <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>原格状态</t>
+  </si>
+  <si>
+    <t>投入小球</t>
+  </si>
+  <si>
+    <t>生成地貌</t>
+  </si>
+  <si>
+    <t>瞬时伤害</t>
+  </si>
+  <si>
+    <t>击退距离(格)</t>
+  </si>
+  <si>
+    <t>麻痹时间(秒)</t>
   </si>
   <si>
     <t>波及范围(格)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发网格连锁</t>
+  </si>
+  <si>
+    <t>基础土</t>
+  </si>
+  <si>
+    <t>纯水</t>
+  </si>
+  <si>
+    <t>普通泥浆</t>
+  </si>
+  <si>
+    <t>FALSE</t>
   </si>
   <si>
     <t>基础水</t>
   </si>
   <si>
-    <t>基础水</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纯水</t>
-  </si>
-  <si>
     <t>纯土</t>
   </si>
   <si>
-    <t>普通泥浆</t>
+    <t>稀泥</t>
   </si>
   <si>
     <t>基础火池</t>
   </si>
   <si>
+    <t>蒸汽</t>
+  </si>
+  <si>
+    <t>陶砖</t>
+  </si>
+  <si>
+    <t>基础电源</t>
+  </si>
+  <si>
+    <t>导电区</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>基础冰面</t>
+  </si>
+  <si>
+    <t>结冰</t>
+  </si>
+  <si>
+    <t>基础植物区</t>
+  </si>
+  <si>
     <t>空地</t>
-  </si>
-  <si>
-    <t>稀泥</t>
-  </si>
-  <si>
-    <t>基础电源</t>
-  </si>
-  <si>
-    <t>基础冰面</t>
-  </si>
-  <si>
-    <t>基础植物区</t>
-  </si>
-  <si>
-    <t>基础土</t>
-  </si>
-  <si>
-    <t>蒸汽</t>
-  </si>
-  <si>
-    <t>陶砖</t>
-  </si>
-  <si>
-    <t>结冰</t>
-  </si>
-  <si>
-    <t>导电区</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,29 +205,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -233,9 +551,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -246,162 +806,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -412,7 +903,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -440,40 +931,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -723,25 +1328,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.3727272727273" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.1272727272727" style="1" customWidth="1"/>
+    <col min="9" max="10" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -767,138 +1372,138 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2" t="s">
+    <row r="5" spans="2:10">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:10">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -906,13 +1511,13 @@
         <v>33</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
@@ -924,21 +1529,21 @@
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:10">
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -953,21 +1558,21 @@
         <v>1.5</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:10">
       <c r="B8" s="1">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="F8" s="1">
         <v>2</v>
@@ -982,21 +1587,21 @@
         <v>1.5</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:10">
       <c r="B9" s="1">
         <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1011,21 +1616,21 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:10">
       <c r="B10" s="1">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
@@ -1040,21 +1645,21 @@
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:10">
       <c r="B11" s="1">
         <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1069,24 +1674,24 @@
         <v>1.5</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:10">
       <c r="B12" s="1">
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -1098,21 +1703,21 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:10">
       <c r="B13" s="1">
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1127,21 +1732,21 @@
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:10">
       <c r="B14" s="1">
         <v>10</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1159,18 +1764,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:10">
       <c r="B15" s="1">
         <v>11</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -1188,18 +1793,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:10">
       <c r="B16" s="1">
         <v>12</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1217,50 +1822,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:10">
       <c r="B17" s="1">
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:10">
       <c r="B18" s="1">
         <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
@@ -1272,20 +1877,20 @@
         <v>1</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576 E1:E1048576" xr:uid="{3185D381-DA91-4C4E-B871-4CFF429EC902}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576 E$1:E$1048576">
       <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{C7F4E47B-FBE5-41F6-8965-69779C735560}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
       <formula1>"纯水,纯土"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E593674-59EC-4505-9460-EBC7FA908D6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819D2C81-4580-4D44-A6A4-24FC708B6D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9960" yWindow="4155" windowWidth="23445" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -1,33 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD93E05D-05D2-409B-A5ED-8E08A8E21608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="14940" windowHeight="9900"/>
+    <workbookView xWindow="14400" yWindow="4860" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -185,18 +183,15 @@
   <si>
     <t>空地</t>
   </si>
+  <si>
+    <t>基础花</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,345 +200,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -551,251 +222,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -810,89 +239,158 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
         </patternFill>
       </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -903,7 +401,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -931,154 +429,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="9"/>
+      <tableStyleElement type="totalRow" dxfId="8"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
+      <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1328,25 +712,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="15" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" style="1" customWidth="1"/>
     <col min="5" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.3727272727273" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.1272727272727" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" style="1" customWidth="1"/>
     <col min="9" max="10" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1378,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1410,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -1442,7 +826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1474,7 +858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1503,7 +887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -1532,7 +916,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -1561,7 +945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -1590,7 +974,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1619,7 +1003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -1648,7 +1032,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -1677,7 +1061,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -1706,7 +1090,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -1735,7 +1119,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -1764,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>11</v>
       </c>
@@ -1793,7 +1177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>12</v>
       </c>
@@ -1822,7 +1206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -1851,7 +1235,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>14</v>
       </c>
@@ -1880,17 +1264,78 @@
         <v>32</v>
       </c>
     </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B19" s="1">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+      <c r="I19" s="1">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B20" s="1">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576 E$1:E$1048576">
-      <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺"</formula1>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺,基础花"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"纯水,纯土"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{F521BDA3-556B-4CDD-B078-B96D141B0D6B}">
+      <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺,基础花"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD93E05D-05D2-409B-A5ED-8E08A8E21608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC83E80E-6ACC-40E2-8990-DB439AB2885F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="4860" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6460" yWindow="1460" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -719,18 +719,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
     <col min="5" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.08984375" style="1" customWidth="1"/>
     <col min="9" max="10" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -794,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -826,7 +826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -858,7 +858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -887,7 +887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -916,7 +916,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -939,13 +939,13 @@
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -1026,13 +1026,13 @@
         <v>1.5</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -1055,13 +1055,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -1084,13 +1084,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>11</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>12</v>
       </c>
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -1229,13 +1229,13 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>14</v>
       </c>
@@ -1258,13 +1258,13 @@
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>15</v>
       </c>
@@ -1287,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="I19" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J19" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>16</v>
       </c>
@@ -1324,18 +1324,15 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576 C1:C1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺,基础花"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"纯水,纯土"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{F521BDA3-556B-4CDD-B078-B96D141B0D6B}">
-      <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺,基础花"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC83E80E-6ACC-40E2-8990-DB439AB2885F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36DE634-C9D2-4347-BBFF-81242EB9079D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="1460" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -718,19 +718,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" customWidth="1"/>
     <col min="5" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.36328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.08984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" style="1" customWidth="1"/>
     <col min="9" max="10" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -794,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -826,7 +826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -858,7 +858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -887,7 +887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -916,7 +916,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -945,7 +945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -974,7 +974,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>11</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>12</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>14</v>
       </c>
@@ -1264,7 +1264,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>15</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>16</v>
       </c>
@@ -1319,6 +1319,64 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B21" s="1">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B22" s="1">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD93E05D-05D2-409B-A5ED-8E08A8E21608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36DE634-C9D2-4347-BBFF-81242EB9079D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="4860" windowWidth="19785" windowHeight="15525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -718,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>32</v>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>32</v>
@@ -1026,7 +1026,7 @@
         <v>1.5</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>41</v>
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>32</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>32</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="1" t="b">
         <v>0</v>
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>32</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>32</v>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J19" s="1" t="b">
         <v>0</v>
@@ -1322,20 +1322,75 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B21" s="1">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
+      <c r="B22" s="1">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576 C1:C1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺,基础花"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"纯水,纯土"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{F521BDA3-556B-4CDD-B078-B96D141B0D6B}">
-      <formula1>"空地,普通泥浆,稀泥,结冰,陶砖,蒸汽,基础水,基础土,基础火池,基础冰面,基础电源,基础植物区,导电区,燎原火海,带电荆棘,霜冻冰刺,基础花"</formula1>
-    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36DE634-C9D2-4347-BBFF-81242EB9079D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9417ADE9-6A6C-43CB-B72F-4E8EE3E3FE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3105" yWindow="3300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="1464" windowWidth="17280" windowHeight="11448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -719,18 +719,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" style="1" customWidth="1"/>
     <col min="9" max="10" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -794,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -826,7 +826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -858,7 +858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -887,7 +887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -916,7 +916,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -945,7 +945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>11</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>12</v>
       </c>
@@ -1194,10 +1194,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -1229,13 +1229,13 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>14</v>
       </c>
@@ -1258,13 +1258,13 @@
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>15</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>16</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>17</v>
       </c>
@@ -1345,13 +1345,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>18</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="1" t="b">
         <v>0</v>

--- a/ConfigWorkspace/Data/element_rule.xlsx
+++ b/ConfigWorkspace/Data/element_rule.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9417ADE9-6A6C-43CB-B72F-4E8EE3E3FE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99398E2-B6F6-4C95-B941-2D74431A828A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="1464" windowWidth="17280" windowHeight="11448" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13875" yWindow="4590" windowWidth="18345" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -719,18 +719,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="1" customWidth="1"/>
     <col min="5" max="6" width="15" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" style="1" customWidth="1"/>
     <col min="9" max="10" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -794,7 +794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
@@ -826,7 +826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -858,7 +858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -887,7 +887,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -916,7 +916,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -930,7 +930,7 @@
         <v>35</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
@@ -945,7 +945,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -974,7 +974,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>43</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
@@ -1061,7 +1061,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>11</v>
       </c>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>12</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -1229,13 +1229,13 @@
         <v>0</v>
       </c>
       <c r="I17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>14</v>
       </c>
@@ -1258,13 +1258,13 @@
         <v>0</v>
       </c>
       <c r="I18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>15</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>16</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>17</v>
       </c>
@@ -1345,13 +1345,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>18</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="1" t="b">
         <v>0</v>
